--- a/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
+++ b/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T14:05:37+00:00</t>
+    <t>2026-05-22T14:31:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1351,7 +1351,7 @@
     <t>Task.input.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-inpatient-medicationrequest)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/eprescription/StructureDefinition/fr-inpatient-medicationrequest)
 </t>
   </si>
   <si>

--- a/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
+++ b/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-analysis-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T14:31:46+00:00</t>
+    <t>2026-05-25T08:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
